--- a/sheets/대금율보/검수/부산민요.xlsx
+++ b/sheets/대금율보/검수/부산민요.xlsx
@@ -25140,7 +25140,7 @@
       </c>
       <c r="T77" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌?</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="U77" s="28" t="inlineStr">
@@ -25344,7 +25344,7 @@
       <c r="Q81" s="22"/>
       <c r="R81" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌?</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="S81" s="28" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="T81" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌?</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="U81" s="28" t="inlineStr">

--- a/sheets/대금율보/검수/부산민요.xlsx
+++ b/sheets/대금율보/검수/부산민요.xlsx
@@ -19987,32 +19987,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="152.99" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="152.99" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="152.99" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="U5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="152.99" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="152.99" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="152.99" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="152.99" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="152.99" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
       </c>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="152.99" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="152.99" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -20814,7 +20814,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="152.99" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="152.99" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -20945,10 +20945,10 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="102.56" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="152.99" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="152.99" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="152.99" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="U19" s="23"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="152.99" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="26"/>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="U20" s="26"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="152.99" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="152.99" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="152.99" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="152.99" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="26"/>
@@ -21604,7 +21604,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="26"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="152.99" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="152.99" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -21732,7 +21732,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="152.99" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="152.99" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -21873,10 +21873,10 @@
       </c>
       <c r="U28" s="26"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="102.56" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="152.99" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -21958,7 +21958,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="152.99" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="U32" s="23"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="152.99" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="152.99" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
       </c>
       <c r="U34" s="26"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="152.99" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="152.99" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="152.99" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="152.99" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="152.99" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
@@ -22521,7 +22521,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="152.99" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="152.99" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="152.99" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="26"/>
@@ -22698,10 +22698,10 @@
       <c r="T42" s="21"/>
       <c r="U42" s="26"/>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="102.56" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="152.99" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
       <c r="T45" s="21"/>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="152.99" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="U46" s="23"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="152.99" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="23"/>
@@ -22978,7 +22978,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="152.99" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
       <c r="T48" s="21"/>
       <c r="U48" s="26"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="152.99" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="152.99" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="24" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="152.99" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="152.99" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="152.99" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="22"/>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="152.99" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="152.99" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
       <c r="T55" s="21"/>
       <c r="U55" s="23"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="152.99" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -23741,10 +23741,10 @@
       </c>
       <c r="U56" s="26"/>
     </row>
-    <row r="57">
+    <row r="57" ht="6.0" customHeight="true">
       <c r="A57" s="0"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="102.56" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="20" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="152.99" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="152.99" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="61" ht="152.99" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21"/>
       <c r="C61" s="23"/>
@@ -24012,7 +24012,7 @@
       <c r="T61" s="21"/>
       <c r="U61" s="23"/>
     </row>
-    <row r="62" ht="56" customHeight="1">
+    <row r="62" ht="152.99" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="152.99" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="152.99" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="U64" s="23"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="152.99" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="152.99" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="152.99" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
       </c>
       <c r="U67" s="22"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="152.99" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="152.99" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="152.99" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21" t="inlineStr">
         <is>
@@ -24856,10 +24856,10 @@
       </c>
       <c r="U70" s="26"/>
     </row>
-    <row r="71">
+    <row r="71" ht="6.0" customHeight="true">
       <c r="A71" s="0"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="102.56" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="20" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
       <c r="T72" s="20"/>
       <c r="U72" s="20"/>
     </row>
-    <row r="73" ht="56" customHeight="1">
+    <row r="73" ht="152.99" customHeight="true">
       <c r="A73" s="0"/>
       <c r="B73" s="21"/>
       <c r="C73" s="22"/>
@@ -24949,7 +24949,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="56" customHeight="1">
+    <row r="74" ht="152.99" customHeight="true">
       <c r="A74" s="0"/>
       <c r="B74" s="21"/>
       <c r="C74" s="23"/>
@@ -25004,7 +25004,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="56" customHeight="1">
+    <row r="75" ht="152.99" customHeight="true">
       <c r="A75" s="0"/>
       <c r="B75" s="21"/>
       <c r="C75" s="23"/>
@@ -25031,7 +25031,7 @@
       <c r="T75" s="21"/>
       <c r="U75" s="23"/>
     </row>
-    <row r="76" ht="56" customHeight="1">
+    <row r="76" ht="152.99" customHeight="true">
       <c r="A76" s="0"/>
       <c r="B76" s="21"/>
       <c r="C76" s="26"/>
@@ -25094,7 +25094,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="56" customHeight="1">
+    <row r="77" ht="152.99" customHeight="true">
       <c r="A77" s="0"/>
       <c r="B77" s="21"/>
       <c r="C77" s="22"/>
@@ -25149,7 +25149,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="56" customHeight="1">
+    <row r="78" ht="152.99" customHeight="true">
       <c r="A78" s="0"/>
       <c r="B78" s="21"/>
       <c r="C78" s="23"/>
@@ -25201,7 +25201,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="56" customHeight="1">
+    <row r="79" ht="152.99" customHeight="true">
       <c r="A79" s="0"/>
       <c r="B79" s="21"/>
       <c r="C79" s="23"/>
@@ -25264,7 +25264,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="56" customHeight="1">
+    <row r="80" ht="152.99" customHeight="true">
       <c r="A80" s="0"/>
       <c r="B80" s="21"/>
       <c r="C80" s="26"/>
@@ -25311,7 +25311,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="56" customHeight="1">
+    <row r="81" ht="152.99" customHeight="true">
       <c r="A81" s="0"/>
       <c r="B81" s="21"/>
       <c r="C81" s="22"/>
@@ -25363,7 +25363,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="56" customHeight="1">
+    <row r="82" ht="152.99" customHeight="true">
       <c r="A82" s="0"/>
       <c r="B82" s="21"/>
       <c r="C82" s="23"/>
@@ -25426,7 +25426,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="56" customHeight="1">
+    <row r="83" ht="152.99" customHeight="true">
       <c r="A83" s="0"/>
       <c r="B83" s="21"/>
       <c r="C83" s="23"/>
@@ -25481,7 +25481,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="56" customHeight="1">
+    <row r="84" ht="152.99" customHeight="true">
       <c r="A84" s="0"/>
       <c r="B84" s="21"/>
       <c r="C84" s="26"/>
@@ -25539,7 +25539,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="5" manualBreakCount="5">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
